--- a/artfynd/A 57222-2024 artfynd.xlsx
+++ b/artfynd/A 57222-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122747680</v>
       </c>
       <c r="B2" t="n">
-        <v>82447</v>
+        <v>82549</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747681</v>
+        <v>122747679</v>
       </c>
       <c r="B3" t="n">
-        <v>98244</v>
+        <v>82549</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>762000</v>
+        <v>762110</v>
       </c>
       <c r="R3" t="n">
-        <v>7227929</v>
+        <v>7227859</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +890,7 @@
         <v>122747678</v>
       </c>
       <c r="B4" t="n">
-        <v>82447</v>
+        <v>82549</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747679</v>
+        <v>122747681</v>
       </c>
       <c r="B5" t="n">
-        <v>82447</v>
+        <v>98347</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,38 +1005,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>762110</v>
+        <v>762000</v>
       </c>
       <c r="R5" t="n">
-        <v>7227859</v>
+        <v>7227929</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 57222-2024 artfynd.xlsx
+++ b/artfynd/A 57222-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122747680</v>
       </c>
       <c r="B2" t="n">
-        <v>82549</v>
+        <v>82553</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122747679</v>
       </c>
       <c r="B3" t="n">
-        <v>82549</v>
+        <v>82553</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>122747678</v>
       </c>
       <c r="B4" t="n">
-        <v>82549</v>
+        <v>82553</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>122747681</v>
       </c>
       <c r="B5" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 57222-2024 artfynd.xlsx
+++ b/artfynd/A 57222-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747680</v>
+        <v>122747679</v>
       </c>
       <c r="B2" t="n">
         <v>82553</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Almetjärnen Ö, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>762105</v>
+        <v>762110</v>
       </c>
       <c r="R2" t="n">
-        <v>7227868</v>
+        <v>7227859</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747679</v>
+        <v>122747678</v>
       </c>
       <c r="B3" t="n">
         <v>82553</v>
@@ -817,14 +817,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Almetjärnen Ö, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>762110</v>
+        <v>762142</v>
       </c>
       <c r="R3" t="n">
-        <v>7227859</v>
+        <v>7227845</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747678</v>
+        <v>122747681</v>
       </c>
       <c r="B4" t="n">
-        <v>82553</v>
+        <v>98355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Almetjärnen Ö, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>762142</v>
+        <v>762000</v>
       </c>
       <c r="R4" t="n">
-        <v>7227845</v>
+        <v>7227929</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747681</v>
+        <v>122747680</v>
       </c>
       <c r="B5" t="n">
-        <v>98355</v>
+        <v>82553</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,38 +1005,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Almetjärnen Ö, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>762000</v>
+        <v>762105</v>
       </c>
       <c r="R5" t="n">
-        <v>7227929</v>
+        <v>7227868</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 57222-2024 artfynd.xlsx
+++ b/artfynd/A 57222-2024 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>122747681</v>
       </c>
       <c r="B4" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 57222-2024 artfynd.xlsx
+++ b/artfynd/A 57222-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747679</v>
+        <v>122747678</v>
       </c>
       <c r="B2" t="n">
         <v>82553</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Almetjärnen Ö, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>762110</v>
+        <v>762142</v>
       </c>
       <c r="R2" t="n">
-        <v>7227859</v>
+        <v>7227845</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747678</v>
+        <v>122747680</v>
       </c>
       <c r="B3" t="n">
         <v>82553</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>762142</v>
+        <v>762105</v>
       </c>
       <c r="R3" t="n">
-        <v>7227845</v>
+        <v>7227868</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747680</v>
+        <v>122747679</v>
       </c>
       <c r="B5" t="n">
         <v>82553</v>
@@ -1029,14 +1029,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Almetjärnen Ö, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>762105</v>
+        <v>762110</v>
       </c>
       <c r="R5" t="n">
-        <v>7227868</v>
+        <v>7227859</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 57222-2024 artfynd.xlsx
+++ b/artfynd/A 57222-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747678</v>
+        <v>122747681</v>
       </c>
       <c r="B2" t="n">
-        <v>82553</v>
+        <v>98365</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Almetjärnen Ö, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>762142</v>
+        <v>762000</v>
       </c>
       <c r="R2" t="n">
-        <v>7227845</v>
+        <v>7227929</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747681</v>
+        <v>122747678</v>
       </c>
       <c r="B4" t="n">
-        <v>98357</v>
+        <v>82553</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Almetjärnen Ö, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>762000</v>
+        <v>762142</v>
       </c>
       <c r="R4" t="n">
-        <v>7227929</v>
+        <v>7227845</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 57222-2024 artfynd.xlsx
+++ b/artfynd/A 57222-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747681</v>
+        <v>122747680</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
+        <v>82553</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Almetjärnen Ö, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>762000</v>
+        <v>762105</v>
       </c>
       <c r="R2" t="n">
-        <v>7227929</v>
+        <v>7227868</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747680</v>
+        <v>122747681</v>
       </c>
       <c r="B3" t="n">
-        <v>82553</v>
+        <v>98365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Almetjärnen Ö, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>762105</v>
+        <v>762000</v>
       </c>
       <c r="R3" t="n">
-        <v>7227868</v>
+        <v>7227929</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 57222-2024 artfynd.xlsx
+++ b/artfynd/A 57222-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747680</v>
+        <v>122747679</v>
       </c>
       <c r="B2" t="n">
         <v>82553</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Almetjärnen Ö, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>762105</v>
+        <v>762110</v>
       </c>
       <c r="R2" t="n">
-        <v>7227868</v>
+        <v>7227859</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747681</v>
+        <v>122747680</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>82553</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Almetjärnen Ö, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>762000</v>
+        <v>762105</v>
       </c>
       <c r="R3" t="n">
-        <v>7227929</v>
+        <v>7227868</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747679</v>
+        <v>122747681</v>
       </c>
       <c r="B5" t="n">
-        <v>82553</v>
+        <v>98365</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,38 +1005,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>762110</v>
+        <v>762000</v>
       </c>
       <c r="R5" t="n">
-        <v>7227859</v>
+        <v>7227929</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 57222-2024 artfynd.xlsx
+++ b/artfynd/A 57222-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747679</v>
+        <v>122747678</v>
       </c>
       <c r="B2" t="n">
         <v>82553</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Almetjärnen Ö, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>762110</v>
+        <v>762142</v>
       </c>
       <c r="R2" t="n">
-        <v>7227859</v>
+        <v>7227845</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747680</v>
+        <v>122747681</v>
       </c>
       <c r="B3" t="n">
-        <v>82553</v>
+        <v>98365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Almetjärnen Ö, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>762105</v>
+        <v>762000</v>
       </c>
       <c r="R3" t="n">
-        <v>7227868</v>
+        <v>7227929</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747678</v>
+        <v>122747680</v>
       </c>
       <c r="B4" t="n">
         <v>82553</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>762142</v>
+        <v>762105</v>
       </c>
       <c r="R4" t="n">
-        <v>7227845</v>
+        <v>7227868</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747681</v>
+        <v>122747679</v>
       </c>
       <c r="B5" t="n">
-        <v>98365</v>
+        <v>82553</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,38 +1005,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>762000</v>
+        <v>762110</v>
       </c>
       <c r="R5" t="n">
-        <v>7227929</v>
+        <v>7227859</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 57222-2024 artfynd.xlsx
+++ b/artfynd/A 57222-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747678</v>
+        <v>122747681</v>
       </c>
       <c r="B2" t="n">
-        <v>82553</v>
+        <v>98365</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Almetjärnen Ö, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>762142</v>
+        <v>762000</v>
       </c>
       <c r="R2" t="n">
-        <v>7227845</v>
+        <v>7227929</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747681</v>
+        <v>122747679</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>82553</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>762000</v>
+        <v>762110</v>
       </c>
       <c r="R3" t="n">
-        <v>7227929</v>
+        <v>7227859</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747680</v>
+        <v>122747678</v>
       </c>
       <c r="B4" t="n">
         <v>82553</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>762105</v>
+        <v>762142</v>
       </c>
       <c r="R4" t="n">
-        <v>7227868</v>
+        <v>7227845</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747679</v>
+        <v>122747680</v>
       </c>
       <c r="B5" t="n">
         <v>82553</v>
@@ -1029,14 +1029,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Almetjärnen Ö, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>762110</v>
+        <v>762105</v>
       </c>
       <c r="R5" t="n">
-        <v>7227859</v>
+        <v>7227868</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 57222-2024 artfynd.xlsx
+++ b/artfynd/A 57222-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747681</v>
+        <v>122747680</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
+        <v>82556</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Almetjärnen Ö, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>762000</v>
+        <v>762105</v>
       </c>
       <c r="R2" t="n">
-        <v>7227929</v>
+        <v>7227868</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747679</v>
+        <v>122747681</v>
       </c>
       <c r="B3" t="n">
-        <v>82553</v>
+        <v>98368</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>762110</v>
+        <v>762000</v>
       </c>
       <c r="R3" t="n">
-        <v>7227859</v>
+        <v>7227929</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747678</v>
+        <v>122747679</v>
       </c>
       <c r="B4" t="n">
-        <v>82553</v>
+        <v>82556</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,14 +923,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Almetjärnen Ö, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>762142</v>
+        <v>762110</v>
       </c>
       <c r="R4" t="n">
-        <v>7227845</v>
+        <v>7227859</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747680</v>
+        <v>122747678</v>
       </c>
       <c r="B5" t="n">
-        <v>82553</v>
+        <v>82556</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>762105</v>
+        <v>762142</v>
       </c>
       <c r="R5" t="n">
-        <v>7227868</v>
+        <v>7227845</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 57222-2024 artfynd.xlsx
+++ b/artfynd/A 57222-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747680</v>
+        <v>122747679</v>
       </c>
       <c r="B2" t="n">
-        <v>82556</v>
+        <v>82558</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Almetjärnen Ö, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>762105</v>
+        <v>762110</v>
       </c>
       <c r="R2" t="n">
-        <v>7227868</v>
+        <v>7227859</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -784,7 +784,7 @@
         <v>122747681</v>
       </c>
       <c r="B3" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747679</v>
+        <v>122747678</v>
       </c>
       <c r="B4" t="n">
-        <v>82556</v>
+        <v>82558</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,14 +923,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Almetjärnen Ö, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>762110</v>
+        <v>762142</v>
       </c>
       <c r="R4" t="n">
-        <v>7227859</v>
+        <v>7227845</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747678</v>
+        <v>122747680</v>
       </c>
       <c r="B5" t="n">
-        <v>82556</v>
+        <v>82558</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>762142</v>
+        <v>762105</v>
       </c>
       <c r="R5" t="n">
-        <v>7227845</v>
+        <v>7227868</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 57222-2024 artfynd.xlsx
+++ b/artfynd/A 57222-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122747679</v>
       </c>
       <c r="B2" t="n">
-        <v>83161</v>
+        <v>83163</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>122747681</v>
       </c>
       <c r="B3" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>122747678</v>
       </c>
       <c r="B4" t="n">
-        <v>83161</v>
+        <v>83163</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>122747680</v>
       </c>
       <c r="B5" t="n">
-        <v>83161</v>
+        <v>83163</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57222-2024 artfynd.xlsx
+++ b/artfynd/A 57222-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122747679</v>
       </c>
       <c r="B2" t="n">
-        <v>83163</v>
+        <v>83165</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>122747681</v>
       </c>
       <c r="B3" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>122747678</v>
       </c>
       <c r="B4" t="n">
-        <v>83163</v>
+        <v>83165</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>122747680</v>
       </c>
       <c r="B5" t="n">
-        <v>83163</v>
+        <v>83165</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57222-2024 artfynd.xlsx
+++ b/artfynd/A 57222-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122747679</v>
       </c>
       <c r="B2" t="n">
-        <v>83165</v>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>122747681</v>
       </c>
       <c r="B3" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>122747678</v>
       </c>
       <c r="B4" t="n">
-        <v>83165</v>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>122747680</v>
       </c>
       <c r="B5" t="n">
-        <v>83165</v>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57222-2024 artfynd.xlsx
+++ b/artfynd/A 57222-2024 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>122747681</v>
       </c>
       <c r="B3" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 57222-2024 artfynd.xlsx
+++ b/artfynd/A 57222-2024 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>122747681</v>
       </c>
       <c r="B3" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 57222-2024 artfynd.xlsx
+++ b/artfynd/A 57222-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747679</v>
+        <v>122747678</v>
       </c>
       <c r="B2" t="n">
-        <v>83180</v>
+        <v>83222</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -706,14 +706,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Almetjärnen Ö, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>762110</v>
+        <v>762142</v>
       </c>
       <c r="R2" t="n">
-        <v>7227859</v>
+        <v>7227845</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,49 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747681</v>
+        <v>122747679</v>
       </c>
       <c r="B3" t="n">
-        <v>99125</v>
+        <v>83222</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>762000</v>
+        <v>762110</v>
       </c>
       <c r="R3" t="n">
-        <v>7227929</v>
+        <v>7227859</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,7 +855,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -882,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747678</v>
+        <v>122747680</v>
       </c>
       <c r="B4" t="n">
-        <v>83180</v>
+        <v>83222</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>762142</v>
+        <v>762105</v>
       </c>
       <c r="R4" t="n">
-        <v>7227845</v>
+        <v>7227868</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,45 +978,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747680</v>
+        <v>122747681</v>
       </c>
       <c r="B5" t="n">
-        <v>83180</v>
+        <v>99195</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Almetjärnen Ö, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>762105</v>
+        <v>762000</v>
       </c>
       <c r="R5" t="n">
-        <v>7227868</v>
+        <v>7227929</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1061,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 57222-2024 artfynd.xlsx
+++ b/artfynd/A 57222-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122747678</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122747679</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122747680</t>
         </is>
       </c>
     </row>
@@ -1081,8 +1101,19 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122747681</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>